--- a/KNK_temp.xlsx
+++ b/KNK_temp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\AMCWN\Documents\GitHub\KontrolaNaczynkaKominka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3DF1F7-ADF5-430D-8395-CDC23DF0F05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6555EAFE-3FD4-4D15-A474-3BC7613568D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,11 +102,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -291,59 +299,53 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -628,175 +630,178 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="32"/>
+    <col min="1" max="16384" width="9.140625" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="32">
+      <c r="A1" s="24">
         <v>15</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="27" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="27" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="32">
+      <c r="A3" s="24">
         <v>11</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="27" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="37">
+      <c r="A4" s="29">
         <v>10</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="28" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="37">
+      <c r="A5" s="29">
         <v>9</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="35" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="28" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="37">
+      <c r="A6" s="29">
         <v>8</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="35" t="s">
+      <c r="B6" s="28"/>
+      <c r="C6" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="28" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="37">
+      <c r="A7" s="29">
         <v>7</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="35" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="28" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="37">
+      <c r="A8" s="29">
         <v>6</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="D8" s="34" t="s">
+      <c r="B8" s="28"/>
+      <c r="D8" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="28" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="37">
+      <c r="A9" s="29">
         <v>5</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="D9" s="34" t="s">
+      <c r="B9" s="28"/>
+      <c r="D9" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="28" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="37">
+      <c r="A10" s="29">
         <v>4</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="E10" s="33" t="s">
+      <c r="B10" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="28" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="37">
+      <c r="A11" s="30">
         <v>3</v>
       </c>
-      <c r="B11" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="33" t="s">
+      <c r="B11" s="30"/>
+      <c r="E11" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="32">
+      <c r="A12" s="24">
         <v>2</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="32">
-        <v>1</v>
-      </c>
-      <c r="E13" s="33" t="s">
+      <c r="A13" s="24">
+        <v>1</v>
+      </c>
+      <c r="E13" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C14" s="35" t="s">
+      <c r="A14" s="24">
+        <v>0</v>
+      </c>
+      <c r="C14" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="24" t="s">
         <v>11</v>
       </c>
     </row>
@@ -842,9 +847,7 @@
       <c r="B2">
         <v>30</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="7"/>
+      <c r="E2" s="6"/>
       <c r="F2">
         <v>0</v>
       </c>
@@ -856,9 +859,7 @@
       <c r="B3">
         <v>29</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="7"/>
+      <c r="E3" s="6"/>
       <c r="F3">
         <v>0</v>
       </c>
@@ -870,9 +871,7 @@
       <c r="B4">
         <v>28</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="7"/>
+      <c r="E4" s="6"/>
       <c r="F4">
         <v>0</v>
       </c>
@@ -884,9 +883,7 @@
       <c r="B5">
         <v>27</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="7"/>
+      <c r="E5" s="6"/>
       <c r="F5">
         <v>0</v>
       </c>
@@ -898,9 +895,7 @@
       <c r="B6" s="1">
         <v>26</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="7"/>
+      <c r="E6" s="6"/>
       <c r="F6">
         <v>0</v>
       </c>
@@ -912,9 +907,7 @@
       <c r="B7" s="1">
         <v>25</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="7"/>
+      <c r="E7" s="6"/>
       <c r="F7">
         <v>0</v>
       </c>
@@ -926,9 +919,7 @@
       <c r="B8" s="1">
         <v>24</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="7"/>
+      <c r="E8" s="6"/>
       <c r="F8">
         <v>0</v>
       </c>
@@ -940,9 +931,7 @@
       <c r="B9" s="1">
         <v>23</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="7"/>
+      <c r="E9" s="6"/>
       <c r="F9">
         <v>0</v>
       </c>
@@ -954,9 +943,7 @@
       <c r="B10" s="1">
         <v>22</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="7"/>
+      <c r="E10" s="6"/>
       <c r="F10">
         <v>0</v>
       </c>
@@ -968,9 +955,7 @@
       <c r="B11" s="1">
         <v>21</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="7"/>
+      <c r="E11" s="6"/>
       <c r="F11">
         <v>0</v>
       </c>
@@ -982,9 +967,7 @@
       <c r="B12" s="1">
         <v>20</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="7"/>
+      <c r="E12" s="6"/>
       <c r="F12">
         <v>0</v>
       </c>
@@ -996,9 +979,7 @@
       <c r="B13" s="1">
         <v>19</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="7"/>
+      <c r="E13" s="6"/>
       <c r="F13">
         <v>0</v>
       </c>
@@ -1010,9 +991,7 @@
       <c r="B14" s="1">
         <v>18</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="7"/>
+      <c r="E14" s="6"/>
       <c r="F14">
         <v>0</v>
       </c>
@@ -1024,9 +1003,7 @@
       <c r="B15" s="1">
         <v>17</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="7"/>
+      <c r="E15" s="6"/>
       <c r="F15">
         <v>0</v>
       </c>
@@ -1038,9 +1015,7 @@
       <c r="B16" s="1">
         <v>16</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="7"/>
+      <c r="E16" s="6"/>
       <c r="F16">
         <v>0</v>
       </c>
@@ -1052,9 +1027,7 @@
       <c r="B17" s="1">
         <v>15</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="7"/>
+      <c r="E17" s="6"/>
       <c r="F17">
         <v>0</v>
       </c>
@@ -1063,160 +1036,150 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <v>14</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="14">
-        <v>0</v>
-      </c>
-      <c r="G18" s="15">
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="13">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="16"/>
-      <c r="B19" s="17">
+      <c r="A19" s="15"/>
+      <c r="B19" s="1">
         <v>13</v>
       </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="21">
-        <v>0</v>
-      </c>
-      <c r="G19" s="22">
+      <c r="D19" s="7"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17">
+      <c r="A20" s="15"/>
+      <c r="B20" s="1">
         <v>12</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="21">
-        <v>0</v>
-      </c>
-      <c r="G20" s="22">
+      <c r="D20" s="7"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="8">
         <v>11</v>
       </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="21">
-        <v>0</v>
-      </c>
-      <c r="G21" s="22">
+      <c r="D21" s="7"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="16"/>
-      <c r="B22" s="17">
+      <c r="A22" s="15"/>
+      <c r="B22" s="1">
         <v>10</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="21">
-        <v>0</v>
-      </c>
-      <c r="G22" s="22">
+      <c r="D22" s="7"/>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="16"/>
-      <c r="B23" s="17">
+      <c r="A23" s="15"/>
+      <c r="B23" s="1">
         <v>9</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="21">
-        <v>0</v>
-      </c>
-      <c r="G23" s="22">
+      <c r="D23" s="7"/>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="24">
+      <c r="A24" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="8">
         <v>8</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="21">
-        <v>0</v>
-      </c>
-      <c r="G24" s="22">
+      <c r="C24" s="5"/>
+      <c r="D24" s="7"/>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="16"/>
-      <c r="B25" s="17">
+      <c r="A25" s="15"/>
+      <c r="B25" s="1">
         <v>7</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="21">
-        <v>0</v>
-      </c>
-      <c r="G25" s="22">
+      <c r="C25" s="5"/>
+      <c r="D25" s="7"/>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="16"/>
-      <c r="B26" s="17">
+      <c r="A26" s="15"/>
+      <c r="B26" s="1">
         <v>6</v>
       </c>
-      <c r="C26" s="25"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="21">
-        <v>0</v>
-      </c>
-      <c r="G26" s="22">
+      <c r="C26" s="5"/>
+      <c r="D26" s="7"/>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="27">
+      <c r="A27" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="19">
         <v>5</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="30">
-        <v>1</v>
-      </c>
-      <c r="G27" s="31">
+      <c r="C27" s="20"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="22">
+        <v>1</v>
+      </c>
+      <c r="G27" s="23">
         <v>1</v>
       </c>
     </row>
@@ -1224,9 +1187,7 @@
       <c r="B28" s="1">
         <v>4</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
+      <c r="C28" s="5"/>
       <c r="F28" s="2">
         <v>1</v>
       </c>
@@ -1238,9 +1199,7 @@
       <c r="B29" s="1">
         <v>3</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
+      <c r="C29" s="5"/>
       <c r="F29" s="2">
         <v>1</v>
       </c>
@@ -1252,12 +1211,10 @@
       <c r="A30" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="8">
         <v>2</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
+      <c r="C30" s="5"/>
       <c r="F30" s="2">
         <v>1</v>
       </c>
@@ -1269,9 +1226,9 @@
       <c r="B31">
         <v>1</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="7"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="6"/>
       <c r="F31" s="2">
         <v>1</v>
       </c>
@@ -1283,9 +1240,9 @@
       <c r="B32">
         <v>0</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="7"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="6"/>
       <c r="F32" s="2">
         <v>1</v>
       </c>
@@ -1294,7 +1251,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
